--- a/data/lossofsale_sg_kottakkal.xlsx
+++ b/data/lossofsale_sg_kottakkal.xlsx
@@ -1540,6 +1540,59 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="65">
+        <v>25</v>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">sinan</t>
+        </is>
+      </c>
+      <c r="D27" s="65">
+        <v>9656633278</v>
+      </c>
+      <c t="inlineStr" r="E27">
+        <is>
+          <t xml:space="preserve">11-04-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F27">
+        <is>
+          <t xml:space="preserve">Siyad vallikkadan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G27">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H27">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I27">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J27">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K27">
+        <is>
+          <t xml:space="preserve">loss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
